--- a/reports/GateGuard_QA_Report.xlsx
+++ b/reports/GateGuard_QA_Report.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="87">
   <si>
     <t>Metric / Component</t>
   </si>
@@ -26,7 +26,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>15/6/2026, 5:11:24 pm</t>
+    <t>15/6/2026, 5:22:06 pm</t>
   </si>
   <si>
     <t>Appium Platform Target</t>
@@ -68,7 +68,7 @@
     <t>Selenium Execution Time</t>
   </si>
   <si>
-    <t>105.15s</t>
+    <t>102.53s</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -89,7 +89,7 @@
     <t>TC-201</t>
   </si>
   <si>
-    <t>GateGuard Web Automation Suite</t>
+    <t>Selenium Web Tests</t>
   </si>
   <si>
     <t>TC-101: Login - Validate empty field constraints</t>
@@ -98,7 +98,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>3.39s</t>
+    <t>3.94s</t>
   </si>
   <si>
     <t>TC-202</t>
@@ -107,7 +107,7 @@
     <t>TC-102: Login - Validate password length restriction</t>
   </si>
   <si>
-    <t>3.11s</t>
+    <t>4.41s</t>
   </si>
   <si>
     <t>TC-203</t>
@@ -116,7 +116,7 @@
     <t>TC-103: Login - Verify successful authentication for Admin role</t>
   </si>
   <si>
-    <t>1.96s</t>
+    <t>6.95s</t>
   </si>
   <si>
     <t>TC-204</t>
@@ -125,7 +125,7 @@
     <t>TC-104: Logout - Validate session clear</t>
   </si>
   <si>
-    <t>2.60s</t>
+    <t>2.93s</t>
   </si>
   <si>
     <t>TC-205</t>
@@ -134,7 +134,7 @@
     <t>TC-105: Registration - Validate empty submission block</t>
   </si>
   <si>
-    <t>2.50s</t>
+    <t>3.43s</t>
   </si>
   <si>
     <t>TC-206</t>
@@ -143,7 +143,7 @@
     <t>TC-106: Registration - Validate password mismatch check</t>
   </si>
   <si>
-    <t>3.19s</t>
+    <t>5.96s</t>
   </si>
   <si>
     <t>TC-207</t>
@@ -152,7 +152,7 @@
     <t>TC-107: Registration - Successful signup and dashboard auto-redirect</t>
   </si>
   <si>
-    <t>2.82s</t>
+    <t>3.62s</t>
   </si>
   <si>
     <t>TC-208</t>
@@ -161,13 +161,16 @@
     <t>TC-108: Dashboard - Verify initial statistical widgets mapping</t>
   </si>
   <si>
+    <t>2.15s</t>
+  </si>
+  <si>
     <t>TC-209</t>
   </si>
   <si>
     <t>TC-109: Dashboard - Verify real-time list search filters</t>
   </si>
   <si>
-    <t>3.03s</t>
+    <t>2.44s</t>
   </si>
   <si>
     <t>TC-210</t>
@@ -176,7 +179,7 @@
     <t>TC-110: Dashboard - Verify "Active" status tab filter</t>
   </si>
   <si>
-    <t>7.28s</t>
+    <t>2.94s</t>
   </si>
   <si>
     <t>TC-211</t>
@@ -185,7 +188,7 @@
     <t>TC-111: Dashboard - Verify "Upcoming" status tab filter</t>
   </si>
   <si>
-    <t>4.67s</t>
+    <t>5.83s</t>
   </si>
   <si>
     <t>TC-212</t>
@@ -194,7 +197,7 @@
     <t>TC-112: Pass Generation - Validate form fields error flags</t>
   </si>
   <si>
-    <t>2.67s</t>
+    <t>2.71s</t>
   </si>
   <si>
     <t>TC-213</t>
@@ -203,7 +206,7 @@
     <t>TC-113: Pass Generation - Complete flow with QR modal trigger</t>
   </si>
   <si>
-    <t>8.79s</t>
+    <t>3.16s</t>
   </si>
   <si>
     <t>TC-214</t>
@@ -212,7 +215,7 @@
     <t>TC-114: Pass Generation - Cancel/Delete active pass</t>
   </si>
   <si>
-    <t>11.48s</t>
+    <t>4.62s</t>
   </si>
   <si>
     <t>TC-215</t>
@@ -221,7 +224,7 @@
     <t>TC-115: QR Preview - Open preview dialog from visitor logs list</t>
   </si>
   <si>
-    <t>3.32s</t>
+    <t>4.66s</t>
   </si>
   <si>
     <t>TC-216</t>
@@ -230,7 +233,7 @@
     <t>TC-116: QR Preview - Validate Pass ID display format</t>
   </si>
   <si>
-    <t>3.77s</t>
+    <t>3.34s</t>
   </si>
   <si>
     <t>TC-217</t>
@@ -239,7 +242,7 @@
     <t>TC-117: QR Preview - Safely close preview modal and restore dashboard focus</t>
   </si>
   <si>
-    <t>2.74s</t>
+    <t>4.98s</t>
   </si>
   <si>
     <t>TC-218</t>
@@ -248,7 +251,7 @@
     <t>TC-118: Profile - Update user info metadata fields</t>
   </si>
   <si>
-    <t>2.94s</t>
+    <t>5.91s</t>
   </si>
   <si>
     <t>TC-219</t>
@@ -257,7 +260,7 @@
     <t>TC-119: Profile - Verify profile roles are in readonly format</t>
   </si>
   <si>
-    <t>3.44s</t>
+    <t>3.49s</t>
   </si>
   <si>
     <t>TC-220</t>
@@ -266,7 +269,7 @@
     <t>TC-120: Profile - Check dashboard layout buttons routing and click download QR</t>
   </si>
   <si>
-    <t>5.31s</t>
+    <t>2.77s</t>
   </si>
   <si>
     <t>Failed Test Name</t>
@@ -1002,211 +1005,211 @@
         <v>26</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1226,10 +1229,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -1249,10 +1252,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/reports/GateGuard_QA_Report.xlsx
+++ b/reports/GateGuard_QA_Report.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="141">
   <si>
     <t>Metric / Component</t>
   </si>
@@ -26,7 +26,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>15/6/2026, 5:22:06 pm</t>
+    <t>6/15/2026, 11:56:10 AM</t>
   </si>
   <si>
     <t>Appium Platform Target</t>
@@ -68,7 +68,7 @@
     <t>Selenium Execution Time</t>
   </si>
   <si>
-    <t>102.53s</t>
+    <t>50.68s</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -98,7 +98,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>3.94s</t>
+    <t>0.30s</t>
   </si>
   <si>
     <t>TC-202</t>
@@ -107,7 +107,7 @@
     <t>TC-102: Login - Validate password length restriction</t>
   </si>
   <si>
-    <t>4.41s</t>
+    <t>0.23s</t>
   </si>
   <si>
     <t>TC-203</t>
@@ -116,7 +116,7 @@
     <t>TC-103: Login - Verify successful authentication for Admin role</t>
   </si>
   <si>
-    <t>6.95s</t>
+    <t>0.28s</t>
   </si>
   <si>
     <t>TC-204</t>
@@ -125,16 +125,13 @@
     <t>TC-104: Logout - Validate session clear</t>
   </si>
   <si>
-    <t>2.93s</t>
-  </si>
-  <si>
     <t>TC-205</t>
   </si>
   <si>
     <t>TC-105: Registration - Validate empty submission block</t>
   </si>
   <si>
-    <t>3.43s</t>
+    <t>0.24s</t>
   </si>
   <si>
     <t>TC-206</t>
@@ -143,52 +140,37 @@
     <t>TC-106: Registration - Validate password mismatch check</t>
   </si>
   <si>
-    <t>5.96s</t>
-  </si>
-  <si>
     <t>TC-207</t>
   </si>
   <si>
     <t>TC-107: Registration - Successful signup and dashboard auto-redirect</t>
   </si>
   <si>
-    <t>3.62s</t>
-  </si>
-  <si>
     <t>TC-208</t>
   </si>
   <si>
     <t>TC-108: Dashboard - Verify initial statistical widgets mapping</t>
   </si>
   <si>
-    <t>2.15s</t>
-  </si>
-  <si>
     <t>TC-209</t>
   </si>
   <si>
     <t>TC-109: Dashboard - Verify real-time list search filters</t>
   </si>
   <si>
-    <t>2.44s</t>
-  </si>
-  <si>
     <t>TC-210</t>
   </si>
   <si>
     <t>TC-110: Dashboard - Verify "Active" status tab filter</t>
   </si>
   <si>
-    <t>2.94s</t>
-  </si>
-  <si>
     <t>TC-211</t>
   </si>
   <si>
     <t>TC-111: Dashboard - Verify "Upcoming" status tab filter</t>
   </si>
   <si>
-    <t>5.83s</t>
+    <t>0.27s</t>
   </si>
   <si>
     <t>TC-212</t>
@@ -197,16 +179,13 @@
     <t>TC-112: Pass Generation - Validate form fields error flags</t>
   </si>
   <si>
-    <t>2.71s</t>
-  </si>
-  <si>
     <t>TC-213</t>
   </si>
   <si>
     <t>TC-113: Pass Generation - Complete flow with QR modal trigger</t>
   </si>
   <si>
-    <t>3.16s</t>
+    <t>0.36s</t>
   </si>
   <si>
     <t>TC-214</t>
@@ -215,7 +194,7 @@
     <t>TC-114: Pass Generation - Cancel/Delete active pass</t>
   </si>
   <si>
-    <t>4.62s</t>
+    <t>0.29s</t>
   </si>
   <si>
     <t>TC-215</t>
@@ -224,34 +203,25 @@
     <t>TC-115: QR Preview - Open preview dialog from visitor logs list</t>
   </si>
   <si>
-    <t>4.66s</t>
-  </si>
-  <si>
     <t>TC-216</t>
   </si>
   <si>
     <t>TC-116: QR Preview - Validate Pass ID display format</t>
   </si>
   <si>
-    <t>3.34s</t>
-  </si>
-  <si>
     <t>TC-217</t>
   </si>
   <si>
     <t>TC-117: QR Preview - Safely close preview modal and restore dashboard focus</t>
   </si>
   <si>
-    <t>4.98s</t>
-  </si>
-  <si>
     <t>TC-218</t>
   </si>
   <si>
     <t>TC-118: Profile - Update user info metadata fields</t>
   </si>
   <si>
-    <t>5.91s</t>
+    <t>0.32s</t>
   </si>
   <si>
     <t>TC-219</t>
@@ -260,16 +230,208 @@
     <t>TC-119: Profile - Verify profile roles are in readonly format</t>
   </si>
   <si>
-    <t>3.49s</t>
-  </si>
-  <si>
     <t>TC-220</t>
   </si>
   <si>
     <t>TC-120: Profile - Check dashboard layout buttons routing and click download QR</t>
   </si>
   <si>
-    <t>2.77s</t>
+    <t>TC-221</t>
+  </si>
+  <si>
+    <t>1.49s</t>
+  </si>
+  <si>
+    <t>TC-222</t>
+  </si>
+  <si>
+    <t>0.51s</t>
+  </si>
+  <si>
+    <t>TC-223</t>
+  </si>
+  <si>
+    <t>0.56s</t>
+  </si>
+  <si>
+    <t>TC-224</t>
+  </si>
+  <si>
+    <t>0.59s</t>
+  </si>
+  <si>
+    <t>TC-225</t>
+  </si>
+  <si>
+    <t>TC-226</t>
+  </si>
+  <si>
+    <t>0.60s</t>
+  </si>
+  <si>
+    <t>TC-227</t>
+  </si>
+  <si>
+    <t>0.63s</t>
+  </si>
+  <si>
+    <t>TC-228</t>
+  </si>
+  <si>
+    <t>TC-229</t>
+  </si>
+  <si>
+    <t>TC-230</t>
+  </si>
+  <si>
+    <t>1.90s</t>
+  </si>
+  <si>
+    <t>TC-231</t>
+  </si>
+  <si>
+    <t>0.75s</t>
+  </si>
+  <si>
+    <t>TC-232</t>
+  </si>
+  <si>
+    <t>0.62s</t>
+  </si>
+  <si>
+    <t>TC-233</t>
+  </si>
+  <si>
+    <t>0.71s</t>
+  </si>
+  <si>
+    <t>TC-234</t>
+  </si>
+  <si>
+    <t>TC-235</t>
+  </si>
+  <si>
+    <t>TC-236</t>
+  </si>
+  <si>
+    <t>TC-237</t>
+  </si>
+  <si>
+    <t>0.77s</t>
+  </si>
+  <si>
+    <t>TC-238</t>
+  </si>
+  <si>
+    <t>0.65s</t>
+  </si>
+  <si>
+    <t>TC-239</t>
+  </si>
+  <si>
+    <t>TC-240</t>
+  </si>
+  <si>
+    <t>3.15s</t>
+  </si>
+  <si>
+    <t>TC-241</t>
+  </si>
+  <si>
+    <t>6.20s</t>
+  </si>
+  <si>
+    <t>TC-242</t>
+  </si>
+  <si>
+    <t>0.87s</t>
+  </si>
+  <si>
+    <t>TC-243</t>
+  </si>
+  <si>
+    <t>0.80s</t>
+  </si>
+  <si>
+    <t>TC-244</t>
+  </si>
+  <si>
+    <t>0.81s</t>
+  </si>
+  <si>
+    <t>TC-245</t>
+  </si>
+  <si>
+    <t>1.11s</t>
+  </si>
+  <si>
+    <t>TC-246</t>
+  </si>
+  <si>
+    <t>TC-247</t>
+  </si>
+  <si>
+    <t>TC-248</t>
+  </si>
+  <si>
+    <t>TC-249</t>
+  </si>
+  <si>
+    <t>0.72s</t>
+  </si>
+  <si>
+    <t>TC-250</t>
+  </si>
+  <si>
+    <t>0.78s</t>
+  </si>
+  <si>
+    <t>TC-251</t>
+  </si>
+  <si>
+    <t>TC-252</t>
+  </si>
+  <si>
+    <t>TC-253</t>
+  </si>
+  <si>
+    <t>1.01s</t>
+  </si>
+  <si>
+    <t>TC-254</t>
+  </si>
+  <si>
+    <t>0.82s</t>
+  </si>
+  <si>
+    <t>TC-255</t>
+  </si>
+  <si>
+    <t>0.84s</t>
+  </si>
+  <si>
+    <t>TC-256</t>
+  </si>
+  <si>
+    <t>0.86s</t>
+  </si>
+  <si>
+    <t>TC-257</t>
+  </si>
+  <si>
+    <t>0.91s</t>
+  </si>
+  <si>
+    <t>TC-258</t>
+  </si>
+  <si>
+    <t>TC-259</t>
+  </si>
+  <si>
+    <t>TC-260</t>
+  </si>
+  <si>
+    <t>0.92s</t>
   </si>
   <si>
     <t>Failed Test Name</t>
@@ -753,7 +915,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="3">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -761,7 +923,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="3">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -846,7 +1008,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -937,279 +1099,959 @@
         <v>26</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>38</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="D7" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>75</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="3" t="s">
+      <c r="B27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E27" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D21" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E21" s="4" t="s">
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
         <v>84</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -1229,10 +2071,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>85</v>
+        <v>139</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>86</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -1252,10 +2094,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>85</v>
+        <v>139</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>86</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/reports/GateGuard_QA_Report.xlsx
+++ b/reports/GateGuard_QA_Report.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="188">
   <si>
     <t>Metric / Component</t>
   </si>
@@ -26,13 +26,13 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>6/15/2026, 11:56:10 AM</t>
+    <t>15/6/2026, 6:02:26 pm</t>
   </si>
   <si>
     <t>Appium Platform Target</t>
   </si>
   <si>
-    <t>Android Device</t>
+    <t>Android Emulator (Simulated)</t>
   </si>
   <si>
     <t>Selenium Browser Target</t>
@@ -62,13 +62,13 @@
     <t>Appium Execution Time</t>
   </si>
   <si>
-    <t>0s</t>
+    <t>0.08s</t>
   </si>
   <si>
     <t>Selenium Execution Time</t>
   </si>
   <si>
-    <t>50.68s</t>
+    <t>580.58s</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -86,6 +86,81 @@
     <t>Execution Duration</t>
   </si>
   <si>
+    <t>TC-101</t>
+  </si>
+  <si>
+    <t>Authentication Testing Suite</t>
+  </si>
+  <si>
+    <t>Should validate constraints for empty fields</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>0.01s</t>
+  </si>
+  <si>
+    <t>TC-102</t>
+  </si>
+  <si>
+    <t>Should show error messages for invalid credentials</t>
+  </si>
+  <si>
+    <t>0.00s</t>
+  </si>
+  <si>
+    <t>TC-103</t>
+  </si>
+  <si>
+    <t>Should successfully navigate on valid login</t>
+  </si>
+  <si>
+    <t>TC-104</t>
+  </si>
+  <si>
+    <t>Should verify session persistence across application restarts</t>
+  </si>
+  <si>
+    <t>TC-105</t>
+  </si>
+  <si>
+    <t>Should successfully log out and clear the session</t>
+  </si>
+  <si>
+    <t>TC-106</t>
+  </si>
+  <si>
+    <t>Navigation Testing Suite</t>
+  </si>
+  <si>
+    <t>Should validate Bottom Navigation Bar tab switching</t>
+  </si>
+  <si>
+    <t>TC-107</t>
+  </si>
+  <si>
+    <t>Should validate Navigation Drawer routing paths</t>
+  </si>
+  <si>
+    <t>TC-108</t>
+  </si>
+  <si>
+    <t>Should validate device Back button actions</t>
+  </si>
+  <si>
+    <t>TC-109</t>
+  </si>
+  <si>
+    <t>Should validate app restart behavior stability</t>
+  </si>
+  <si>
+    <t>TC-110</t>
+  </si>
+  <si>
+    <t>Should validate Deep Linking URLs redirects</t>
+  </si>
+  <si>
     <t>TC-201</t>
   </si>
   <si>
@@ -95,10 +170,7 @@
     <t>TC-101: Login - Validate empty field constraints</t>
   </si>
   <si>
-    <t>PASS</t>
-  </si>
-  <si>
-    <t>0.30s</t>
+    <t>8.18s</t>
   </si>
   <si>
     <t>TC-202</t>
@@ -107,7 +179,7 @@
     <t>TC-102: Login - Validate password length restriction</t>
   </si>
   <si>
-    <t>0.23s</t>
+    <t>3.34s</t>
   </si>
   <si>
     <t>TC-203</t>
@@ -116,7 +188,7 @@
     <t>TC-103: Login - Verify successful authentication for Admin role</t>
   </si>
   <si>
-    <t>0.28s</t>
+    <t>4.99s</t>
   </si>
   <si>
     <t>TC-204</t>
@@ -125,13 +197,16 @@
     <t>TC-104: Logout - Validate session clear</t>
   </si>
   <si>
+    <t>4.19s</t>
+  </si>
+  <si>
     <t>TC-205</t>
   </si>
   <si>
     <t>TC-105: Registration - Validate empty submission block</t>
   </si>
   <si>
-    <t>0.24s</t>
+    <t>3.73s</t>
   </si>
   <si>
     <t>TC-206</t>
@@ -140,37 +215,52 @@
     <t>TC-106: Registration - Validate password mismatch check</t>
   </si>
   <si>
+    <t>5.01s</t>
+  </si>
+  <si>
     <t>TC-207</t>
   </si>
   <si>
     <t>TC-107: Registration - Successful signup and dashboard auto-redirect</t>
   </si>
   <si>
+    <t>3.81s</t>
+  </si>
+  <si>
     <t>TC-208</t>
   </si>
   <si>
     <t>TC-108: Dashboard - Verify initial statistical widgets mapping</t>
   </si>
   <si>
+    <t>3.59s</t>
+  </si>
+  <si>
     <t>TC-209</t>
   </si>
   <si>
     <t>TC-109: Dashboard - Verify real-time list search filters</t>
   </si>
   <si>
+    <t>2.35s</t>
+  </si>
+  <si>
     <t>TC-210</t>
   </si>
   <si>
     <t>TC-110: Dashboard - Verify "Active" status tab filter</t>
   </si>
   <si>
+    <t>4.32s</t>
+  </si>
+  <si>
     <t>TC-211</t>
   </si>
   <si>
     <t>TC-111: Dashboard - Verify "Upcoming" status tab filter</t>
   </si>
   <si>
-    <t>0.27s</t>
+    <t>2.78s</t>
   </si>
   <si>
     <t>TC-212</t>
@@ -179,13 +269,16 @@
     <t>TC-112: Pass Generation - Validate form fields error flags</t>
   </si>
   <si>
+    <t>6.68s</t>
+  </si>
+  <si>
     <t>TC-213</t>
   </si>
   <si>
     <t>TC-113: Pass Generation - Complete flow with QR modal trigger</t>
   </si>
   <si>
-    <t>0.36s</t>
+    <t>4.68s</t>
   </si>
   <si>
     <t>TC-214</t>
@@ -194,7 +287,7 @@
     <t>TC-114: Pass Generation - Cancel/Delete active pass</t>
   </si>
   <si>
-    <t>0.29s</t>
+    <t>2.14s</t>
   </si>
   <si>
     <t>TC-215</t>
@@ -203,25 +296,34 @@
     <t>TC-115: QR Preview - Open preview dialog from visitor logs list</t>
   </si>
   <si>
+    <t>2.25s</t>
+  </si>
+  <si>
     <t>TC-216</t>
   </si>
   <si>
     <t>TC-116: QR Preview - Validate Pass ID display format</t>
   </si>
   <si>
+    <t>2.54s</t>
+  </si>
+  <si>
     <t>TC-217</t>
   </si>
   <si>
     <t>TC-117: QR Preview - Safely close preview modal and restore dashboard focus</t>
   </si>
   <si>
+    <t>2.32s</t>
+  </si>
+  <si>
     <t>TC-218</t>
   </si>
   <si>
     <t>TC-118: Profile - Update user info metadata fields</t>
   </si>
   <si>
-    <t>0.32s</t>
+    <t>2.68s</t>
   </si>
   <si>
     <t>TC-219</t>
@@ -230,6 +332,9 @@
     <t>TC-119: Profile - Verify profile roles are in readonly format</t>
   </si>
   <si>
+    <t>2.46s</t>
+  </si>
+  <si>
     <t>TC-220</t>
   </si>
   <si>
@@ -239,187 +344,223 @@
     <t>TC-221</t>
   </si>
   <si>
-    <t>1.49s</t>
+    <t>7.31s</t>
   </si>
   <si>
     <t>TC-222</t>
   </si>
   <si>
-    <t>0.51s</t>
+    <t>2.64s</t>
   </si>
   <si>
     <t>TC-223</t>
   </si>
   <si>
-    <t>0.56s</t>
+    <t>5.41s</t>
   </si>
   <si>
     <t>TC-224</t>
   </si>
   <si>
-    <t>0.59s</t>
+    <t>3.23s</t>
   </si>
   <si>
     <t>TC-225</t>
   </si>
   <si>
+    <t>3.05s</t>
+  </si>
+  <si>
     <t>TC-226</t>
   </si>
   <si>
-    <t>0.60s</t>
+    <t>2.95s</t>
   </si>
   <si>
     <t>TC-227</t>
   </si>
   <si>
-    <t>0.63s</t>
+    <t>3.40s</t>
   </si>
   <si>
     <t>TC-228</t>
   </si>
   <si>
+    <t>3.32s</t>
+  </si>
+  <si>
     <t>TC-229</t>
   </si>
   <si>
+    <t>3.12s</t>
+  </si>
+  <si>
     <t>TC-230</t>
   </si>
   <si>
-    <t>1.90s</t>
+    <t>9.86s</t>
   </si>
   <si>
     <t>TC-231</t>
   </si>
   <si>
-    <t>0.75s</t>
+    <t>4.26s</t>
   </si>
   <si>
     <t>TC-232</t>
   </si>
   <si>
-    <t>0.62s</t>
+    <t>3.38s</t>
   </si>
   <si>
     <t>TC-233</t>
   </si>
   <si>
-    <t>0.71s</t>
+    <t>3.95s</t>
   </si>
   <si>
     <t>TC-234</t>
   </si>
   <si>
+    <t>3.29s</t>
+  </si>
+  <si>
     <t>TC-235</t>
   </si>
   <si>
+    <t>6.57s</t>
+  </si>
+  <si>
     <t>TC-236</t>
   </si>
   <si>
+    <t>3.45s</t>
+  </si>
+  <si>
     <t>TC-237</t>
   </si>
   <si>
-    <t>0.77s</t>
+    <t>3.44s</t>
   </si>
   <si>
     <t>TC-238</t>
   </si>
   <si>
-    <t>0.65s</t>
+    <t>3.53s</t>
   </si>
   <si>
     <t>TC-239</t>
   </si>
   <si>
+    <t>9.15s</t>
+  </si>
+  <si>
     <t>TC-240</t>
   </si>
   <si>
-    <t>3.15s</t>
+    <t>15.39s</t>
   </si>
   <si>
     <t>TC-241</t>
   </si>
   <si>
-    <t>6.20s</t>
+    <t>7.26s</t>
   </si>
   <si>
     <t>TC-242</t>
   </si>
   <si>
-    <t>0.87s</t>
+    <t>5.50s</t>
   </si>
   <si>
     <t>TC-243</t>
   </si>
   <si>
-    <t>0.80s</t>
+    <t>5.47s</t>
   </si>
   <si>
     <t>TC-244</t>
   </si>
   <si>
-    <t>0.81s</t>
+    <t>5.32s</t>
   </si>
   <si>
     <t>TC-245</t>
   </si>
   <si>
-    <t>1.11s</t>
+    <t>5.91s</t>
   </si>
   <si>
     <t>TC-246</t>
   </si>
   <si>
+    <t>6.85s</t>
+  </si>
+  <si>
     <t>TC-247</t>
   </si>
   <si>
+    <t>6.24s</t>
+  </si>
+  <si>
     <t>TC-248</t>
   </si>
   <si>
+    <t>5.83s</t>
+  </si>
+  <si>
     <t>TC-249</t>
   </si>
   <si>
-    <t>0.72s</t>
+    <t>4.96s</t>
   </si>
   <si>
     <t>TC-250</t>
   </si>
   <si>
-    <t>0.78s</t>
+    <t>6.36s</t>
   </si>
   <si>
     <t>TC-251</t>
   </si>
   <si>
+    <t>6.33s</t>
+  </si>
+  <si>
     <t>TC-252</t>
   </si>
   <si>
+    <t>6.16s</t>
+  </si>
+  <si>
     <t>TC-253</t>
   </si>
   <si>
-    <t>1.01s</t>
+    <t>7.88s</t>
   </si>
   <si>
     <t>TC-254</t>
   </si>
   <si>
-    <t>0.82s</t>
+    <t>6.05s</t>
   </si>
   <si>
     <t>TC-255</t>
   </si>
   <si>
-    <t>0.84s</t>
+    <t>7.00s</t>
   </si>
   <si>
     <t>TC-256</t>
   </si>
   <si>
-    <t>0.86s</t>
+    <t>6.30s</t>
   </si>
   <si>
     <t>TC-257</t>
   </si>
   <si>
-    <t>0.91s</t>
+    <t>6.81s</t>
   </si>
   <si>
     <t>TC-258</t>
@@ -431,7 +572,7 @@
     <t>TC-260</t>
   </si>
   <si>
-    <t>0.92s</t>
+    <t>8.14s</t>
   </si>
   <si>
     <t>Failed Test Name</t>
@@ -915,7 +1056,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="3">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -923,7 +1064,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="3">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -974,7 +1115,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -998,6 +1139,176 @@
       </c>
       <c r="E1" s="1" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1036,1022 +1347,1022 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>33</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>59</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>51</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>51</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>64</v>
+        <v>97</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>27</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>67</v>
+        <v>101</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>68</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>69</v>
+        <v>103</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>59</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>71</v>
+        <v>106</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>74</v>
+        <v>109</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>80</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>78</v>
+        <v>117</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>83</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>85</v>
+        <v>121</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>85</v>
+        <v>123</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>87</v>
+        <v>124</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>90</v>
+        <v>128</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>91</v>
+        <v>129</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>92</v>
+        <v>130</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>93</v>
+        <v>131</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>94</v>
+        <v>132</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>95</v>
+        <v>133</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>96</v>
+        <v>134</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>85</v>
+        <v>135</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>85</v>
+        <v>137</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>98</v>
+        <v>138</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>85</v>
+        <v>139</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>100</v>
+        <v>141</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>67</v>
-      </c>
       <c r="D39" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>102</v>
+        <v>143</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>103</v>
+        <v>144</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>85</v>
+        <v>145</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>104</v>
+        <v>146</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>105</v>
+        <v>147</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>106</v>
+        <v>148</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>107</v>
+        <v>149</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>108</v>
+        <v>150</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>109</v>
+        <v>151</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>110</v>
+        <v>152</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>111</v>
+        <v>153</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>112</v>
+        <v>154</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>113</v>
+        <v>155</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>114</v>
+        <v>156</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>115</v>
+        <v>157</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>116</v>
+        <v>158</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>109</v>
+        <v>159</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>109</v>
+        <v>161</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>118</v>
+        <v>162</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>100</v>
+        <v>163</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>119</v>
+        <v>164</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>120</v>
+        <v>165</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>121</v>
+        <v>166</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="D51" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>123</v>
+        <v>168</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>122</v>
+        <v>169</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>124</v>
+        <v>170</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>113</v>
+        <v>171</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>125</v>
+        <v>172</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>126</v>
+        <v>173</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>127</v>
+        <v>174</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="D55" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>128</v>
+        <v>175</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="D56" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>130</v>
+        <v>177</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>131</v>
+        <v>178</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="D57" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>132</v>
+        <v>179</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>133</v>
+        <v>180</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="D58" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>134</v>
+        <v>181</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>135</v>
+        <v>182</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>67</v>
+        <v>101</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>109</v>
+        <v>181</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>136</v>
+        <v>183</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>128</v>
+        <v>157</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>137</v>
+        <v>184</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>138</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -2071,10 +2382,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>139</v>
+        <v>186</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>140</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -2094,10 +2405,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>139</v>
+        <v>186</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>140</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>

--- a/reports/GateGuard_QA_Report.xlsx
+++ b/reports/GateGuard_QA_Report.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="171">
   <si>
     <t>Metric / Component</t>
   </si>
@@ -26,7 +26,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>15/6/2026, 6:02:26 pm</t>
+    <t>6/15/2026, 12:36:40 PM</t>
   </si>
   <si>
     <t>Appium Platform Target</t>
@@ -62,13 +62,13 @@
     <t>Appium Execution Time</t>
   </si>
   <si>
-    <t>0.08s</t>
+    <t>0.03s</t>
   </si>
   <si>
     <t>Selenium Execution Time</t>
   </si>
   <si>
-    <t>580.58s</t>
+    <t>70.23s</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -98,7 +98,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>0.01s</t>
+    <t>0.00s</t>
   </si>
   <si>
     <t>TC-102</t>
@@ -107,9 +107,6 @@
     <t>Should show error messages for invalid credentials</t>
   </si>
   <si>
-    <t>0.00s</t>
-  </si>
-  <si>
     <t>TC-103</t>
   </si>
   <si>
@@ -170,7 +167,7 @@
     <t>TC-101: Login - Validate empty field constraints</t>
   </si>
   <si>
-    <t>8.18s</t>
+    <t>0.39s</t>
   </si>
   <si>
     <t>TC-202</t>
@@ -179,7 +176,7 @@
     <t>TC-102: Login - Validate password length restriction</t>
   </si>
   <si>
-    <t>3.34s</t>
+    <t>0.34s</t>
   </si>
   <si>
     <t>TC-203</t>
@@ -188,7 +185,7 @@
     <t>TC-103: Login - Verify successful authentication for Admin role</t>
   </si>
   <si>
-    <t>4.99s</t>
+    <t>0.36s</t>
   </si>
   <si>
     <t>TC-204</t>
@@ -197,16 +194,13 @@
     <t>TC-104: Logout - Validate session clear</t>
   </si>
   <si>
-    <t>4.19s</t>
-  </si>
-  <si>
     <t>TC-205</t>
   </si>
   <si>
     <t>TC-105: Registration - Validate empty submission block</t>
   </si>
   <si>
-    <t>3.73s</t>
+    <t>0.37s</t>
   </si>
   <si>
     <t>TC-206</t>
@@ -215,34 +209,25 @@
     <t>TC-106: Registration - Validate password mismatch check</t>
   </si>
   <si>
-    <t>5.01s</t>
-  </si>
-  <si>
     <t>TC-207</t>
   </si>
   <si>
     <t>TC-107: Registration - Successful signup and dashboard auto-redirect</t>
   </si>
   <si>
-    <t>3.81s</t>
-  </si>
-  <si>
     <t>TC-208</t>
   </si>
   <si>
     <t>TC-108: Dashboard - Verify initial statistical widgets mapping</t>
   </si>
   <si>
-    <t>3.59s</t>
-  </si>
-  <si>
     <t>TC-209</t>
   </si>
   <si>
     <t>TC-109: Dashboard - Verify real-time list search filters</t>
   </si>
   <si>
-    <t>2.35s</t>
+    <t>0.33s</t>
   </si>
   <si>
     <t>TC-210</t>
@@ -251,7 +236,7 @@
     <t>TC-110: Dashboard - Verify "Active" status tab filter</t>
   </si>
   <si>
-    <t>4.32s</t>
+    <t>0.38s</t>
   </si>
   <si>
     <t>TC-211</t>
@@ -260,16 +245,13 @@
     <t>TC-111: Dashboard - Verify "Upcoming" status tab filter</t>
   </si>
   <si>
-    <t>2.78s</t>
-  </si>
-  <si>
     <t>TC-212</t>
   </si>
   <si>
     <t>TC-112: Pass Generation - Validate form fields error flags</t>
   </si>
   <si>
-    <t>6.68s</t>
+    <t>0.40s</t>
   </si>
   <si>
     <t>TC-213</t>
@@ -278,7 +260,7 @@
     <t>TC-113: Pass Generation - Complete flow with QR modal trigger</t>
   </si>
   <si>
-    <t>4.68s</t>
+    <t>0.46s</t>
   </si>
   <si>
     <t>TC-214</t>
@@ -287,34 +269,25 @@
     <t>TC-114: Pass Generation - Cancel/Delete active pass</t>
   </si>
   <si>
-    <t>2.14s</t>
-  </si>
-  <si>
     <t>TC-215</t>
   </si>
   <si>
     <t>TC-115: QR Preview - Open preview dialog from visitor logs list</t>
   </si>
   <si>
-    <t>2.25s</t>
-  </si>
-  <si>
     <t>TC-216</t>
   </si>
   <si>
     <t>TC-116: QR Preview - Validate Pass ID display format</t>
   </si>
   <si>
-    <t>2.54s</t>
-  </si>
-  <si>
     <t>TC-217</t>
   </si>
   <si>
     <t>TC-117: QR Preview - Safely close preview modal and restore dashboard focus</t>
   </si>
   <si>
-    <t>2.32s</t>
+    <t>0.41s</t>
   </si>
   <si>
     <t>TC-218</t>
@@ -323,18 +296,12 @@
     <t>TC-118: Profile - Update user info metadata fields</t>
   </si>
   <si>
-    <t>2.68s</t>
-  </si>
-  <si>
     <t>TC-219</t>
   </si>
   <si>
     <t>TC-119: Profile - Verify profile roles are in readonly format</t>
   </si>
   <si>
-    <t>2.46s</t>
-  </si>
-  <si>
     <t>TC-220</t>
   </si>
   <si>
@@ -344,223 +311,202 @@
     <t>TC-221</t>
   </si>
   <si>
-    <t>7.31s</t>
+    <t>1.86s</t>
   </si>
   <si>
     <t>TC-222</t>
   </si>
   <si>
-    <t>2.64s</t>
+    <t>0.58s</t>
   </si>
   <si>
     <t>TC-223</t>
   </si>
   <si>
-    <t>5.41s</t>
+    <t>0.63s</t>
   </si>
   <si>
     <t>TC-224</t>
   </si>
   <si>
-    <t>3.23s</t>
+    <t>0.68s</t>
   </si>
   <si>
     <t>TC-225</t>
   </si>
   <si>
-    <t>3.05s</t>
+    <t>0.56s</t>
   </si>
   <si>
     <t>TC-226</t>
   </si>
   <si>
-    <t>2.95s</t>
-  </si>
-  <si>
     <t>TC-227</t>
   </si>
   <si>
-    <t>3.40s</t>
+    <t>0.69s</t>
   </si>
   <si>
     <t>TC-228</t>
   </si>
   <si>
-    <t>3.32s</t>
-  </si>
-  <si>
     <t>TC-229</t>
   </si>
   <si>
-    <t>3.12s</t>
+    <t>0.64s</t>
   </si>
   <si>
     <t>TC-230</t>
   </si>
   <si>
-    <t>9.86s</t>
+    <t>1.95s</t>
   </si>
   <si>
     <t>TC-231</t>
   </si>
   <si>
-    <t>4.26s</t>
+    <t>0.88s</t>
   </si>
   <si>
     <t>TC-232</t>
   </si>
   <si>
-    <t>3.38s</t>
+    <t>0.73s</t>
   </si>
   <si>
     <t>TC-233</t>
   </si>
   <si>
-    <t>3.95s</t>
+    <t>0.77s</t>
   </si>
   <si>
     <t>TC-234</t>
   </si>
   <si>
-    <t>3.29s</t>
+    <t>0.72s</t>
   </si>
   <si>
     <t>TC-235</t>
   </si>
   <si>
-    <t>6.57s</t>
+    <t>0.65s</t>
   </si>
   <si>
     <t>TC-236</t>
   </si>
   <si>
-    <t>3.45s</t>
+    <t>0.92s</t>
   </si>
   <si>
     <t>TC-237</t>
   </si>
   <si>
-    <t>3.44s</t>
-  </si>
-  <si>
     <t>TC-238</t>
   </si>
   <si>
-    <t>3.53s</t>
+    <t>0.70s</t>
   </si>
   <si>
     <t>TC-239</t>
   </si>
   <si>
-    <t>9.15s</t>
+    <t>0.66s</t>
   </si>
   <si>
     <t>TC-240</t>
   </si>
   <si>
-    <t>15.39s</t>
+    <t>3.07s</t>
   </si>
   <si>
     <t>TC-241</t>
   </si>
   <si>
-    <t>7.26s</t>
+    <t>8.40s</t>
   </si>
   <si>
     <t>TC-242</t>
   </si>
   <si>
-    <t>5.50s</t>
+    <t>1.01s</t>
   </si>
   <si>
     <t>TC-243</t>
   </si>
   <si>
-    <t>5.47s</t>
+    <t>0.85s</t>
   </si>
   <si>
     <t>TC-244</t>
   </si>
   <si>
-    <t>5.32s</t>
+    <t>0.90s</t>
   </si>
   <si>
     <t>TC-245</t>
   </si>
   <si>
-    <t>5.91s</t>
+    <t>1.26s</t>
   </si>
   <si>
     <t>TC-246</t>
   </si>
   <si>
-    <t>6.85s</t>
-  </si>
-  <si>
     <t>TC-247</t>
   </si>
   <si>
-    <t>6.24s</t>
-  </si>
-  <si>
     <t>TC-248</t>
   </si>
   <si>
-    <t>5.83s</t>
+    <t>0.81s</t>
   </si>
   <si>
     <t>TC-249</t>
   </si>
   <si>
-    <t>4.96s</t>
+    <t>0.78s</t>
   </si>
   <si>
     <t>TC-250</t>
   </si>
   <si>
-    <t>6.36s</t>
+    <t>0.86s</t>
   </si>
   <si>
     <t>TC-251</t>
   </si>
   <si>
-    <t>6.33s</t>
+    <t>0.83s</t>
   </si>
   <si>
     <t>TC-252</t>
   </si>
   <si>
-    <t>6.16s</t>
+    <t>0.89s</t>
   </si>
   <si>
     <t>TC-253</t>
   </si>
   <si>
-    <t>7.88s</t>
+    <t>1.11s</t>
   </si>
   <si>
     <t>TC-254</t>
   </si>
   <si>
-    <t>6.05s</t>
-  </si>
-  <si>
     <t>TC-255</t>
   </si>
   <si>
-    <t>7.00s</t>
+    <t>0.94s</t>
   </si>
   <si>
     <t>TC-256</t>
   </si>
   <si>
-    <t>6.30s</t>
-  </si>
-  <si>
     <t>TC-257</t>
   </si>
   <si>
-    <t>6.81s</t>
+    <t>0.98s</t>
   </si>
   <si>
     <t>TC-258</t>
@@ -569,10 +515,13 @@
     <t>TC-259</t>
   </si>
   <si>
+    <t>1.03s</t>
+  </si>
+  <si>
     <t>TC-260</t>
   </si>
   <si>
-    <t>8.14s</t>
+    <t>1.20s</t>
   </si>
   <si>
     <t>Failed Test Name</t>
@@ -1172,143 +1121,143 @@
         <v>26</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>39</v>
-      </c>
       <c r="D7" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="D8" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="D9" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="D10" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="D11" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1347,1022 +1296,1022 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>50</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>53</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="D5" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>61</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>90</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>93</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>102</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>105</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>102</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="D22" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>123</v>
+        <v>102</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="B42" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C42" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="D42" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>159</v>
+        <v>126</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D51" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D55" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="D56" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D57" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="D58" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -2382,10 +2331,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -2405,10 +2354,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
